--- a/output/laminas_comunales/comunal_i_peringrmin_a_2024_aysen.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2024_aysen.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -405,9 +400,6 @@
       <c r="E2">
         <v>41.78217821782179</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +419,6 @@
       <c r="E3">
         <v>85.71428571428572</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -449,9 +438,6 @@
       <c r="E4">
         <v>-18.96243291592128</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -471,9 +457,6 @@
       <c r="E5">
         <v>64.92537313432834</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,9 +476,6 @@
       <c r="E6">
         <v>48.95104895104896</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -515,9 +495,6 @@
       <c r="E7">
         <v>35.31353135313531</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -537,9 +514,6 @@
       <c r="E8">
         <v>24.40677966101694</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,9 +533,6 @@
       <c r="E9">
         <v>12.37458193979932</v>
       </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -581,9 +552,6 @@
       <c r="E10">
         <v>26.4</v>
       </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -602,9 +570,6 @@
       </c>
       <c r="E11">
         <v>13.67521367521369</v>
-      </c>
-      <c r="F11" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_peringrmin_a_2024_aysen.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2024_aysen.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -461,7 +461,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="B6">
@@ -518,57 +518,76 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Chile Chico</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B9">
-        <v>3.36</v>
+        <v>3.56</v>
       </c>
       <c r="C9">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="D9">
-        <v>0.3699999999999997</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E9">
-        <v>12.37458193979932</v>
+        <v>24.0418118466899</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Chile Chico</t>
         </is>
       </c>
       <c r="B10">
-        <v>3.16</v>
+        <v>3.36</v>
       </c>
       <c r="C10">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="D10">
-        <v>0.6600000000000001</v>
+        <v>0.3699999999999997</v>
       </c>
       <c r="E10">
-        <v>26.4</v>
+        <v>12.37458193979932</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>3.16</v>
+      </c>
+      <c r="C11">
+        <v>2.5</v>
+      </c>
+      <c r="D11">
+        <v>0.6600000000000001</v>
+      </c>
+      <c r="E11">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Cisnes</t>
         </is>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>2.66</v>
       </c>
-      <c r="C11">
+      <c r="C12">
         <v>2.34</v>
       </c>
-      <c r="D11">
+      <c r="D12">
         <v>0.3200000000000003</v>
       </c>
-      <c r="E11">
+      <c r="E12">
         <v>13.67521367521369</v>
       </c>
     </row>
@@ -667,7 +686,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="B9">

--- a/output/laminas_comunales/comunal_i_peringrmin_a_2024_aysen.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2024_aysen.xlsx
@@ -598,7 +598,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -607,20 +607,12 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aysén</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>3.16</v>
+          <t>Río Ibáñez</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -629,88 +621,61 @@
           <t>Chile Chico</t>
         </is>
       </c>
-      <c r="B3">
-        <v>3.36</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cisnes</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>2.66</v>
+          <t>Lago Verde</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cochrane</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>4.42</v>
+          <t>Coyhaique</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coyhaique</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>3.67</v>
+          <t>Cisnes</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Guaitecas</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>4.1</v>
+          <t>Tortel</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lago Verde</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>7.16</v>
+          <t>O'Higgins</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>4.26</v>
+          <t>Cochrane</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Río Ibáñez</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>4.53</v>
+          <t>Guaitecas</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tortel</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>5.59</v>
+          <t>Aysén</t>
+        </is>
       </c>
     </row>
   </sheetData>
